--- a/02_Inventory/画面モックアップ.xlsx
+++ b/02_Inventory/画面モックアップ.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yu-sugino\Downloads\workspace\14_extratask\01_Attendance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yu-sugino\Downloads\workspace\14_extratask\02_Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EC7953-C3A8-4076-B8B8-67EAFD1DCAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE1AF54-4DE6-4446-ADDE-33BFF284A621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{39A8802C-C3B2-4A09-96CE-5C3180BFF5B5}"/>
+    <workbookView xWindow="3384" yWindow="3384" windowWidth="17280" windowHeight="9960" activeTab="2" xr2:uid="{39A8802C-C3B2-4A09-96CE-5C3180BFF5B5}"/>
   </bookViews>
   <sheets>
     <sheet name="メイン画面" sheetId="1" r:id="rId1"/>
@@ -282,11 +282,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4170,8 +4167,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="85000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
       </xdr:spPr>
@@ -4649,16 +4647,15 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="670560" y="3657600"/>
-          <a:ext cx="2011680" cy="457201"/>
+          <a:off x="665408" y="3606085"/>
+          <a:ext cx="1996226" cy="450761"/>
         </a:xfrm>
         <a:prstGeom prst="snipRoundRect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </xdr:spPr>
@@ -5995,7 +5992,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E867B3FF-783D-436D-8C77-B835BBEBF4EB}">
-  <dimension ref="S15:Z44"/>
+  <dimension ref="S30:Z44"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="5" max="5" width="3.59765625" customWidth="1"/>
@@ -6008,411 +6005,393 @@
     <col min="26" max="26" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="19:25" x14ac:dyDescent="0.45">
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-    </row>
-    <row r="16" spans="19:25" x14ac:dyDescent="0.45">
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-    </row>
     <row r="30" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S30" s="4" t="s">
+      <c r="S30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="T30" s="4" t="s">
+      <c r="T30" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="U30" s="4" t="s">
+      <c r="U30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="V30" s="4" t="s">
+      <c r="V30" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W30" s="4" t="s">
+      <c r="W30" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X30" s="4" t="s">
+      <c r="X30" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y30" s="4" t="s">
+      <c r="Y30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="Z30" s="4" t="s">
+      <c r="Z30" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="31" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S31" s="2" t="s">
+      <c r="S31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="T31" s="2" t="s">
+      <c r="T31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U31" s="2" t="s">
+      <c r="U31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="V31" s="2">
+      <c r="V31" s="1">
         <v>15</v>
       </c>
-      <c r="W31" s="2" t="s">
+      <c r="W31" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="X31" s="2" t="s">
+      <c r="X31" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y31" s="3">
+      <c r="Y31" s="2">
         <v>46143</v>
       </c>
-      <c r="Z31" s="2" t="s">
+      <c r="Z31" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="32" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S32" s="2" t="s">
+      <c r="S32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="T32" s="2" t="s">
+      <c r="T32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="U32" s="2" t="s">
+      <c r="U32" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="V32" s="2">
+      <c r="V32" s="1">
         <v>10</v>
       </c>
-      <c r="W32" s="2" t="s">
+      <c r="W32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="X32" s="2" t="s">
+      <c r="X32" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="2">
         <v>46143</v>
       </c>
-      <c r="Z32" s="2" t="s">
+      <c r="Z32" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="33" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S33" s="2" t="s">
+      <c r="S33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T33" s="2" t="s">
+      <c r="T33" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="U33" s="2" t="s">
+      <c r="U33" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V33" s="2">
+      <c r="V33" s="1">
         <v>55</v>
       </c>
-      <c r="W33" s="2" t="s">
+      <c r="W33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="X33" s="2" t="s">
+      <c r="X33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Y33" s="2">
         <v>46147</v>
       </c>
-      <c r="Z33" s="2" t="s">
+      <c r="Z33" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="34" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y34" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z34" s="2" t="s">
+      <c r="S34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z34" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="35" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z35" s="2" t="s">
+      <c r="S35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z35" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="36" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z36" s="2" t="s">
+      <c r="S36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z36" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="37" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y37" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z37" s="2" t="s">
+      <c r="S37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z37" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="38" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z38" s="2" t="s">
+      <c r="S38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z38" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="39" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y39" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z39" s="2" t="s">
+      <c r="S39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y39" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z39" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="40" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z40" s="2" t="s">
+      <c r="S40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z40" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="41" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z41" s="2" t="s">
+      <c r="S41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z41" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="42" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z42" s="2" t="s">
+      <c r="S42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z42" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="43" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z43" s="2" t="s">
+      <c r="S43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y43" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z43" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="44" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y44" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z44" s="2" t="s">
+      <c r="S44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z44" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -6425,7 +6404,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DDBB369-7ECA-4129-9293-6E71DC1D9AE2}">
-  <dimension ref="S15:Z44"/>
+  <dimension ref="S30:Z44"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="5" max="5" width="3.59765625" customWidth="1"/>
@@ -6438,395 +6417,377 @@
     <col min="26" max="26" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="19:25" x14ac:dyDescent="0.45">
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-    </row>
-    <row r="16" spans="19:25" x14ac:dyDescent="0.45">
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-    </row>
     <row r="30" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S30" s="4" t="s">
+      <c r="S30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="T30" s="4" t="s">
+      <c r="T30" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="U30" s="4" t="s">
+      <c r="U30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="V30" s="4" t="s">
+      <c r="V30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W30" s="4" t="s">
+      <c r="W30" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="X30" s="4" t="s">
+      <c r="X30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="4"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
     </row>
     <row r="31" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S31" s="2" t="s">
+      <c r="S31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="T31" s="2" t="s">
+      <c r="T31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U31" s="2" t="s">
+      <c r="U31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="V31" s="2">
+      <c r="V31" s="1">
         <v>55</v>
       </c>
-      <c r="W31" s="2">
+      <c r="W31" s="1">
         <v>6</v>
       </c>
-      <c r="X31" s="3">
+      <c r="X31" s="2">
         <v>46151</v>
       </c>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="1"/>
     </row>
     <row r="32" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S32" s="2" t="s">
+      <c r="S32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="T32" s="2" t="s">
+      <c r="T32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="U32" s="2" t="s">
+      <c r="U32" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="V32" s="2">
+      <c r="V32" s="1">
         <v>24</v>
       </c>
-      <c r="W32" s="2" t="s">
+      <c r="W32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="X32" s="3">
+      <c r="X32" s="2">
         <v>46151</v>
       </c>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="2"/>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="1"/>
     </row>
     <row r="33" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S33" s="2" t="s">
+      <c r="S33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T33" s="2" t="s">
+      <c r="T33" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="U33" s="2" t="s">
+      <c r="U33" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V33" s="2">
+      <c r="V33" s="1">
         <v>72</v>
       </c>
-      <c r="W33" s="2">
+      <c r="W33" s="1">
         <v>55</v>
       </c>
-      <c r="X33" s="3">
+      <c r="X33" s="2">
         <v>46151</v>
       </c>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="2"/>
+      <c r="Y33" s="2"/>
+      <c r="Z33" s="1"/>
     </row>
     <row r="34" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y34" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z34" s="2" t="s">
+      <c r="S34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z34" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="35" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z35" s="2" t="s">
+      <c r="S35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z35" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="36" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z36" s="2" t="s">
+      <c r="S36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z36" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="37" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y37" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z37" s="2" t="s">
+      <c r="S37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z37" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="38" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z38" s="2" t="s">
+      <c r="S38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z38" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="39" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y39" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z39" s="2" t="s">
+      <c r="S39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y39" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z39" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="40" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z40" s="2" t="s">
+      <c r="S40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z40" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="41" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z41" s="2" t="s">
+      <c r="S41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z41" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="42" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X42" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z42" s="2" t="s">
+      <c r="S42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z42" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="43" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z43" s="2" t="s">
+      <c r="S43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y43" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z43" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="44" spans="19:26" ht="24.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="S44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y44" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z44" s="2" t="s">
+      <c r="S44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z44" s="1" t="s">
         <v>23</v>
       </c>
     </row>
